--- a/testakten/erbrecht-pflichtteilsergaenzung-niesbrauch-depot-sylt/xlsx/pflichtteilsergaenzung_wertband.xlsx
+++ b/testakten/erbrecht-pflichtteilsergaenzung-niesbrauch-depot-sylt/xlsx/pflichtteilsergaenzung_wertband.xlsx
@@ -9,8 +9,13 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Immobilie" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Depot" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nachlass" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Immobilie'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Depot'!$A$1:$G$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Nachlass'!$A$1:$E$7</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,16 +31,31 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0017324D"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +63,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00CFD6DA"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,74 +445,119 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="39" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Datum</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Wert brutto</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Nießbrauchwert</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Streitpunkt</t>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stichtag</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Wert unbelastet EUR</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Nießbrauch / Rechte EUR</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Nettowert Arbeit EUR</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Quelle</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Kommentar</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>03.02.2018</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="2" t="n">
         <v>1450000</v>
       </c>
-      <c r="C2" t="n">
-        <v>420000</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Lebenserwartung und Miete</t>
+      <c r="C2" s="2" t="n">
+        <v>-420000</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1030000</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Gutachterkurzbrief</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>nur Spanne</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Alter, Miete und Lastentragung prüfen</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>14.01.2026</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="2" t="n">
         <v>1780000</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Todestag</t>
+      <c r="D3" s="2" t="n">
+        <v>1780000</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Gutachterkurzbrief</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>nur Spanne</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Todestag; keine Rechtsberechnung</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -492,98 +568,532 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Datum</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Vorgang</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Betrag</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Empfänger</t>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Betrag EUR</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Von</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>An</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Quelle</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Offene Frage</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>17.09.2021</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Kurswert vor Übertrag</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>312460.35</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Helga</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Helga</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Bankauskunft</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Stichtagswert</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>18.09.2021</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Depotübertrag</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>240000</v>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>unentgeltlicher Depotübertrag</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>312460.35</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Helga</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Theo</t>
         </is>
       </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Übertragsauftrag</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Ertragsabrede</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>10.12.2021</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2106.4</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Theo</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Helga</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Bankbuchung</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Ertrag oder Unterstützung</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>14.06.2022</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>2840</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Theo</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Helga</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Bankbuchung</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Ertrag oder Unterstützung</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>12.12.2022</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>2840</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Theo</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Helga</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Bankbuchung</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Ertrag oder Unterstützung</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>16.06.2023</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>3120</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Theo</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Helga</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Bankbuchung</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Ertrag oder Unterstützung</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>15.12.2023</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>3120</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Theo</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Helga</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Bankbuchung</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Ertrag oder Unterstützung</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>14.06.2024</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>3300</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Theo</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Helga</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Bankbuchung</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Text Unterstützung Oma</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Betrag EUR</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Quelle</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Belegstatus</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Offene Frage</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Bankguthaben</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>48310</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Privates Verzeichnis / Bank</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>teilweise</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>weitere Konten</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>31.12.2022</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Zinsgutschrift</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>3200</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Helga Konto</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Hausrat</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Karsten</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>pauschal</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Inventar</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>31.12.2023</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Zinsgutschrift</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>2900</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Helga Konto</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Schmuck</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Karsten</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Versicherung nennt Goldarmreif</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Bewertung</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Bestattung</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>-12840</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Rechnung</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>belegt</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Erstattungen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Steuererstattung</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Anja</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Bescheid</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Ferienmieten Dezember 2025</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Agentur</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>offen</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Abrechnung</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>